--- a/public/static/工序导入模板.xlsx
+++ b/public/static/工序导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工序导入" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工序编码(</t>
     </r>
     <r>
@@ -59,6 +66,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工序名称(</t>
     </r>
     <r>
@@ -109,6 +123,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>加工类型(</t>
     </r>
     <r>
@@ -148,9 +169,6 @@
     <t>超精</t>
   </si>
   <si>
-    <t>套圈</t>
-  </si>
-  <si>
     <t>自制</t>
   </si>
   <si>
@@ -167,6 +185,9 @@
   </si>
   <si>
     <t>3、工序类型：正常工序、测振工序、热处理工序</t>
+  </si>
+  <si>
+    <t>4、工序分类(必填)：填写工序分类编码</t>
   </si>
 </sst>
 </file>
@@ -1415,15 +1436,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.11111111111111" customWidth="1"/>
-    <col min="2" max="2" width="21.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="7.10833333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.225" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="20.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="20.5555555555556" customWidth="1"/>
-    <col min="6" max="6" width="18.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="31.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="20.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="20.5583333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.775" customWidth="1"/>
+    <col min="7" max="7" width="31.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
@@ -1459,14 +1480,12 @@
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -1479,29 +1498,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="82.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="82.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
     </row>
